--- a/modelos/perfis/fundo-municipal-de-educacao/molde_padrao.xlsx
+++ b/modelos/perfis/fundo-municipal-de-educacao/molde_padrao.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG24"/>
+  <dimension ref="A1:AG26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1153,132 +1153,101 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" s="7">
-        <f>SUM(B6:B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="7">
-        <f>SUM(C6:C9)</f>
-        <v/>
-      </c>
-      <c r="D10" s="7">
-        <f>SUM(D6:D9)</f>
-        <v/>
-      </c>
-      <c r="E10" s="7">
-        <f>SUM(E6:E9)</f>
-        <v/>
-      </c>
-      <c r="F10" s="7">
-        <f>SUM(F6:F9)</f>
-        <v/>
-      </c>
-      <c r="G10" s="7">
-        <f>SUM(G6:G9)</f>
-        <v/>
-      </c>
-      <c r="H10" s="7">
-        <f>SUM(H6:H9)</f>
-        <v/>
-      </c>
-      <c r="I10" s="7">
-        <f>SUM(I6:I9)</f>
-        <v/>
-      </c>
-      <c r="J10" s="7">
-        <f>SUM(J6:J9)</f>
-        <v/>
-      </c>
-      <c r="K10" s="7">
-        <f>SUM(K6:K9)</f>
-        <v/>
-      </c>
-      <c r="L10" s="7">
-        <f>SUM(L6:L9)</f>
-        <v/>
-      </c>
-      <c r="M10" s="7">
-        <f>SUM(M6:M9)</f>
-        <v/>
-      </c>
-      <c r="N10" s="7">
-        <f>SUM(N6:N9)</f>
-        <v/>
-      </c>
-      <c r="O10" s="7">
-        <f>SUM(O6:O9)</f>
-        <v/>
-      </c>
-      <c r="P10" s="7">
-        <f>SUM(P6:P9)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="7">
-        <f>SUM(Q6:Q9)</f>
-        <v/>
-      </c>
-      <c r="R10" s="7">
-        <f>SUM(R6:R9)</f>
-        <v/>
-      </c>
-      <c r="S10" s="7">
-        <f>SUM(S6:S9)</f>
-        <v/>
-      </c>
-      <c r="T10" s="7">
-        <f>SUM(T6:T9)</f>
-        <v/>
-      </c>
-      <c r="U10" s="7">
-        <f>SUM(U6:U9)</f>
-        <v/>
-      </c>
-      <c r="V10" s="7">
-        <f>SUM(V6:V9)</f>
-        <v/>
-      </c>
-      <c r="W10" s="7">
-        <f>SUM(W6:W9)</f>
-        <v/>
-      </c>
-      <c r="X10" s="7">
-        <f>SUM(X6:X9)</f>
-        <v/>
-      </c>
-      <c r="Y10" s="7">
-        <f>SUM(Y6:Y9)</f>
-        <v/>
-      </c>
-      <c r="Z10" s="7">
-        <f>SUM(Z6:Z9)</f>
-        <v/>
-      </c>
-      <c r="AA10" s="7">
-        <f>SUM(AA6:AA9)</f>
-        <v/>
-      </c>
-      <c r="AB10" s="7">
-        <f>SUM(AB6:AB9)</f>
-        <v/>
-      </c>
-      <c r="AC10" s="7">
-        <f>SUM(AC6:AC9)</f>
-        <v/>
-      </c>
-      <c r="AD10" s="7">
-        <f>SUM(AD6:AD9)</f>
-        <v/>
-      </c>
-      <c r="AE10" s="7">
-        <f>SUM(AE6:AE9)</f>
-        <v/>
-      </c>
-      <c r="AF10" s="7">
-        <f>SUM(AF6:AF9)</f>
-        <v/>
+          <t>Complementar</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="AG10" s="7">
         <f>SUM(B10:AF10)</f>
@@ -1286,481 +1255,512 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="N11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="O11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="P11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="Q11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="R11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="S11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="T11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="U11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="V11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="W11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="X11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="Y11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="Z11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="AA11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="AB11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="AC11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="AD11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="AE11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="AF11" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 30%</t>
-        </is>
-      </c>
-      <c r="AG11" s="8" t="n"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B11" s="7">
+        <f>SUM(B6:B10)</f>
+        <v/>
+      </c>
+      <c r="C11" s="7">
+        <f>SUM(C6:C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="7">
+        <f>SUM(D6:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="7">
+        <f>SUM(E6:E10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="7">
+        <f>SUM(F6:F10)</f>
+        <v/>
+      </c>
+      <c r="G11" s="7">
+        <f>SUM(G6:G10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="7">
+        <f>SUM(H6:H10)</f>
+        <v/>
+      </c>
+      <c r="I11" s="7">
+        <f>SUM(I6:I10)</f>
+        <v/>
+      </c>
+      <c r="J11" s="7">
+        <f>SUM(J6:J10)</f>
+        <v/>
+      </c>
+      <c r="K11" s="7">
+        <f>SUM(K6:K10)</f>
+        <v/>
+      </c>
+      <c r="L11" s="7">
+        <f>SUM(L6:L10)</f>
+        <v/>
+      </c>
+      <c r="M11" s="7">
+        <f>SUM(M6:M10)</f>
+        <v/>
+      </c>
+      <c r="N11" s="7">
+        <f>SUM(N6:N10)</f>
+        <v/>
+      </c>
+      <c r="O11" s="7">
+        <f>SUM(O6:O10)</f>
+        <v/>
+      </c>
+      <c r="P11" s="7">
+        <f>SUM(P6:P10)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="7">
+        <f>SUM(Q6:Q10)</f>
+        <v/>
+      </c>
+      <c r="R11" s="7">
+        <f>SUM(R6:R10)</f>
+        <v/>
+      </c>
+      <c r="S11" s="7">
+        <f>SUM(S6:S10)</f>
+        <v/>
+      </c>
+      <c r="T11" s="7">
+        <f>SUM(T6:T10)</f>
+        <v/>
+      </c>
+      <c r="U11" s="7">
+        <f>SUM(U6:U10)</f>
+        <v/>
+      </c>
+      <c r="V11" s="7">
+        <f>SUM(V6:V10)</f>
+        <v/>
+      </c>
+      <c r="W11" s="7">
+        <f>SUM(W6:W10)</f>
+        <v/>
+      </c>
+      <c r="X11" s="7">
+        <f>SUM(X6:X10)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="7">
+        <f>SUM(Y6:Y10)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="7">
+        <f>SUM(Z6:Z10)</f>
+        <v/>
+      </c>
+      <c r="AA11" s="7">
+        <f>SUM(AA6:AA10)</f>
+        <v/>
+      </c>
+      <c r="AB11" s="7">
+        <f>SUM(AB6:AB10)</f>
+        <v/>
+      </c>
+      <c r="AC11" s="7">
+        <f>SUM(AC6:AC10)</f>
+        <v/>
+      </c>
+      <c r="AD11" s="7">
+        <f>SUM(AD6:AD10)</f>
+        <v/>
+      </c>
+      <c r="AE11" s="7">
+        <f>SUM(AE6:AE10)</f>
+        <v/>
+      </c>
+      <c r="AF11" s="7">
+        <f>SUM(AF6:AF10)</f>
+        <v/>
+      </c>
+      <c r="AG11" s="7">
+        <f>SUM(B11:AF11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="8" t="n"/>
-      <c r="O12" s="8" t="n"/>
-      <c r="P12" s="8" t="n"/>
-      <c r="Q12" s="8" t="n"/>
-      <c r="R12" s="8" t="n"/>
-      <c r="S12" s="8" t="n"/>
-      <c r="T12" s="8" t="n"/>
-      <c r="U12" s="8" t="n"/>
-      <c r="V12" s="8" t="n"/>
-      <c r="W12" s="8" t="n"/>
-      <c r="X12" s="8" t="n"/>
-      <c r="Y12" s="8" t="n"/>
-      <c r="Z12" s="8" t="n"/>
-      <c r="AA12" s="8" t="n"/>
-      <c r="AB12" s="8" t="n"/>
-      <c r="AC12" s="8" t="n"/>
-      <c r="AD12" s="8" t="n"/>
-      <c r="AE12" s="8" t="n"/>
-      <c r="AF12" s="8" t="n"/>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="Q12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="T12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="U12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="V12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="X12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="Y12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="Z12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="AA12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="AB12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="AC12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="AD12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="AE12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
+      <c r="AF12" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 30%</t>
+        </is>
+      </c>
       <c r="AG12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+      <c r="M13" s="8" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="8" t="n"/>
+      <c r="S13" s="8" t="n"/>
+      <c r="T13" s="8" t="n"/>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="n"/>
+      <c r="Y13" s="8" t="n"/>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="n"/>
+      <c r="AD13" s="8" t="n"/>
+      <c r="AE13" s="8" t="n"/>
+      <c r="AF13" s="8" t="n"/>
+      <c r="AG13" s="8" t="n"/>
     </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>ARSEM</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>CEF</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>IRRF S/ 13º SALÁRIO</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>IR</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>SINTEGO</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>SINDSAUDE</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>ITAU</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>BRADESCO</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>FUNPRECOR</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>SINDCASE</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>INSS S/ 13º SALÁRIO</t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>INSS</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>IPARV</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>FUNPREV</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>FUMPRU</t>
         </is>
       </c>
-      <c r="Q14" s="3" t="inlineStr">
+      <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>DETERMINAÇÃO JUDICIAL</t>
         </is>
       </c>
-      <c r="R14" s="3" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>EMP. PREV.</t>
         </is>
       </c>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="S15" s="3" t="inlineStr">
         <is>
           <t>PREVPLAN</t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="T15" s="3" t="inlineStr">
         <is>
           <t>IPASI</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t>PARAUNAPREV</t>
         </is>
       </c>
-      <c r="V14" s="3" t="inlineStr">
+      <c r="V15" s="3" t="inlineStr">
         <is>
           <t>BRASILPREV</t>
         </is>
       </c>
-      <c r="W14" s="3" t="inlineStr">
+      <c r="W15" s="3" t="inlineStr">
         <is>
           <t>PREVJUS</t>
         </is>
       </c>
-      <c r="X14" s="3" t="inlineStr">
+      <c r="X15" s="3" t="inlineStr">
         <is>
           <t>AURIPREVI</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
+      <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>FUNPRES</t>
         </is>
       </c>
-      <c r="Z14" s="3" t="inlineStr">
+      <c r="Z15" s="3" t="inlineStr">
         <is>
           <t>PREVFAINA</t>
         </is>
       </c>
-      <c r="AA14" s="3" t="inlineStr">
+      <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>PALMEIRASPREV</t>
         </is>
       </c>
-      <c r="AB14" s="3" t="inlineStr">
+      <c r="AB15" s="3" t="inlineStr">
         <is>
           <t>PREVIBELOS</t>
         </is>
       </c>
-      <c r="AC14" s="3" t="inlineStr">
+      <c r="AC15" s="3" t="inlineStr">
         <is>
           <t>IPASGO</t>
         </is>
       </c>
-      <c r="AD14" s="3" t="inlineStr">
+      <c r="AD15" s="3" t="inlineStr">
         <is>
           <t>IPASGO DEPENDENTES</t>
         </is>
       </c>
-      <c r="AE14" s="3" t="inlineStr">
+      <c r="AE15" s="3" t="inlineStr">
         <is>
           <t>BB - BRASIL</t>
         </is>
       </c>
-      <c r="AF14" s="3" t="inlineStr">
+      <c r="AF15" s="3" t="inlineStr">
         <is>
           <t>DEVOLUÇÃO DE AD. 13°</t>
         </is>
       </c>
-      <c r="AG14" s="3" t="inlineStr">
+      <c r="AG15" s="3" t="inlineStr">
         <is>
           <t>TOTAL DO EVENTO</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Mensal</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="7">
-        <f>SUM(B15:AF15)</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>13º salário</t>
+          <t>Mensal</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
@@ -1864,7 +1864,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Férias</t>
+          <t>13º salário</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
@@ -1968,7 +1968,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Rescisão</t>
+          <t>Férias</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
@@ -2072,132 +2072,101 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B19" s="7">
-        <f>SUM(B15:B18)</f>
-        <v/>
-      </c>
-      <c r="C19" s="7">
-        <f>SUM(C15:C18)</f>
-        <v/>
-      </c>
-      <c r="D19" s="7">
-        <f>SUM(D15:D18)</f>
-        <v/>
-      </c>
-      <c r="E19" s="7">
-        <f>SUM(E15:E18)</f>
-        <v/>
-      </c>
-      <c r="F19" s="7">
-        <f>SUM(F15:F18)</f>
-        <v/>
-      </c>
-      <c r="G19" s="7">
-        <f>SUM(G15:G18)</f>
-        <v/>
-      </c>
-      <c r="H19" s="7">
-        <f>SUM(H15:H18)</f>
-        <v/>
-      </c>
-      <c r="I19" s="7">
-        <f>SUM(I15:I18)</f>
-        <v/>
-      </c>
-      <c r="J19" s="7">
-        <f>SUM(J15:J18)</f>
-        <v/>
-      </c>
-      <c r="K19" s="7">
-        <f>SUM(K15:K18)</f>
-        <v/>
-      </c>
-      <c r="L19" s="7">
-        <f>SUM(L15:L18)</f>
-        <v/>
-      </c>
-      <c r="M19" s="7">
-        <f>SUM(M15:M18)</f>
-        <v/>
-      </c>
-      <c r="N19" s="7">
-        <f>SUM(N15:N18)</f>
-        <v/>
-      </c>
-      <c r="O19" s="7">
-        <f>SUM(O15:O18)</f>
-        <v/>
-      </c>
-      <c r="P19" s="7">
-        <f>SUM(P15:P18)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="7">
-        <f>SUM(Q15:Q18)</f>
-        <v/>
-      </c>
-      <c r="R19" s="7">
-        <f>SUM(R15:R18)</f>
-        <v/>
-      </c>
-      <c r="S19" s="7">
-        <f>SUM(S15:S18)</f>
-        <v/>
-      </c>
-      <c r="T19" s="7">
-        <f>SUM(T15:T18)</f>
-        <v/>
-      </c>
-      <c r="U19" s="7">
-        <f>SUM(U15:U18)</f>
-        <v/>
-      </c>
-      <c r="V19" s="7">
-        <f>SUM(V15:V18)</f>
-        <v/>
-      </c>
-      <c r="W19" s="7">
-        <f>SUM(W15:W18)</f>
-        <v/>
-      </c>
-      <c r="X19" s="7">
-        <f>SUM(X15:X18)</f>
-        <v/>
-      </c>
-      <c r="Y19" s="7">
-        <f>SUM(Y15:Y18)</f>
-        <v/>
-      </c>
-      <c r="Z19" s="7">
-        <f>SUM(Z15:Z18)</f>
-        <v/>
-      </c>
-      <c r="AA19" s="7">
-        <f>SUM(AA15:AA18)</f>
-        <v/>
-      </c>
-      <c r="AB19" s="7">
-        <f>SUM(AB15:AB18)</f>
-        <v/>
-      </c>
-      <c r="AC19" s="7">
-        <f>SUM(AC15:AC18)</f>
-        <v/>
-      </c>
-      <c r="AD19" s="7">
-        <f>SUM(AD15:AD18)</f>
-        <v/>
-      </c>
-      <c r="AE19" s="7">
-        <f>SUM(AE15:AE18)</f>
-        <v/>
-      </c>
-      <c r="AF19" s="7">
-        <f>SUM(AF15:AF18)</f>
-        <v/>
+          <t>Rescisão</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="AG19" s="7">
         <f>SUM(B19:AF19)</f>
@@ -2205,509 +2174,748 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="M20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="N20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="O20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="P20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="Q20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="R20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="S20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="T20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="U20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="V20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="X20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="Y20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="Z20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="AA20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="AB20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="AC20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="AD20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="AE20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="AF20" s="9" t="inlineStr">
-        <is>
-          <t>FUNDEB 70%</t>
-        </is>
-      </c>
-      <c r="AG20" s="8" t="n"/>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Complementar</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="7">
+        <f>SUM(B20:AF20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="8" t="n"/>
-      <c r="M21" s="8" t="n"/>
-      <c r="N21" s="8" t="n"/>
-      <c r="O21" s="8" t="n"/>
-      <c r="P21" s="8" t="n"/>
-      <c r="Q21" s="8" t="n"/>
-      <c r="R21" s="8" t="n"/>
-      <c r="S21" s="8" t="n"/>
-      <c r="T21" s="8" t="n"/>
-      <c r="U21" s="8" t="n"/>
-      <c r="V21" s="8" t="n"/>
-      <c r="W21" s="8" t="n"/>
-      <c r="X21" s="8" t="n"/>
-      <c r="Y21" s="8" t="n"/>
-      <c r="Z21" s="8" t="n"/>
-      <c r="AA21" s="8" t="n"/>
-      <c r="AB21" s="8" t="n"/>
-      <c r="AC21" s="8" t="n"/>
-      <c r="AD21" s="8" t="n"/>
-      <c r="AE21" s="8" t="n"/>
-      <c r="AF21" s="8" t="n"/>
-      <c r="AG21" s="8" t="n"/>
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B21" s="7">
+        <f>SUM(B16:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="7">
+        <f>SUM(C16:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="7">
+        <f>SUM(D16:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="7">
+        <f>SUM(E16:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="7">
+        <f>SUM(F16:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="7">
+        <f>SUM(G16:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="7">
+        <f>SUM(H16:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="7">
+        <f>SUM(I16:I20)</f>
+        <v/>
+      </c>
+      <c r="J21" s="7">
+        <f>SUM(J16:J20)</f>
+        <v/>
+      </c>
+      <c r="K21" s="7">
+        <f>SUM(K16:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="7">
+        <f>SUM(L16:L20)</f>
+        <v/>
+      </c>
+      <c r="M21" s="7">
+        <f>SUM(M16:M20)</f>
+        <v/>
+      </c>
+      <c r="N21" s="7">
+        <f>SUM(N16:N20)</f>
+        <v/>
+      </c>
+      <c r="O21" s="7">
+        <f>SUM(O16:O20)</f>
+        <v/>
+      </c>
+      <c r="P21" s="7">
+        <f>SUM(P16:P20)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="7">
+        <f>SUM(Q16:Q20)</f>
+        <v/>
+      </c>
+      <c r="R21" s="7">
+        <f>SUM(R16:R20)</f>
+        <v/>
+      </c>
+      <c r="S21" s="7">
+        <f>SUM(S16:S20)</f>
+        <v/>
+      </c>
+      <c r="T21" s="7">
+        <f>SUM(T16:T20)</f>
+        <v/>
+      </c>
+      <c r="U21" s="7">
+        <f>SUM(U16:U20)</f>
+        <v/>
+      </c>
+      <c r="V21" s="7">
+        <f>SUM(V16:V20)</f>
+        <v/>
+      </c>
+      <c r="W21" s="7">
+        <f>SUM(W16:W20)</f>
+        <v/>
+      </c>
+      <c r="X21" s="7">
+        <f>SUM(X16:X20)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="7">
+        <f>SUM(Y16:Y20)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="7">
+        <f>SUM(Z16:Z20)</f>
+        <v/>
+      </c>
+      <c r="AA21" s="7">
+        <f>SUM(AA16:AA20)</f>
+        <v/>
+      </c>
+      <c r="AB21" s="7">
+        <f>SUM(AB16:AB20)</f>
+        <v/>
+      </c>
+      <c r="AC21" s="7">
+        <f>SUM(AC16:AC20)</f>
+        <v/>
+      </c>
+      <c r="AD21" s="7">
+        <f>SUM(AD16:AD20)</f>
+        <v/>
+      </c>
+      <c r="AE21" s="7">
+        <f>SUM(AE16:AE20)</f>
+        <v/>
+      </c>
+      <c r="AF21" s="7">
+        <f>SUM(AF16:AF20)</f>
+        <v/>
+      </c>
+      <c r="AG21" s="7">
+        <f>SUM(B21:AF21)</f>
+        <v/>
+      </c>
     </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>ARSEM</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>CEF</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>IRRF S/ 13º SALÁRIO</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>IR</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>SINTEGO</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>SINDSAUDE</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>ITAU</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>BRADESCO</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>FUNPRECOR</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>SINDCASE</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>INSS S/ 13º SALÁRIO</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>INSS</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>IPARV</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>FUNPREV</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t>FUMPRU</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t>DETERMINAÇÃO JUDICIAL</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>EMP. PREV.</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>PREVPLAN</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t>IPASI</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t>PARAUNAPREV</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t>BRASILPREV</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t>PREVJUS</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t>AURIPREVI</t>
-        </is>
-      </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>FUNPRES</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t>PREVFAINA</t>
-        </is>
-      </c>
-      <c r="AA22" s="3" t="inlineStr">
-        <is>
-          <t>PALMEIRASPREV</t>
-        </is>
-      </c>
-      <c r="AB22" s="3" t="inlineStr">
-        <is>
-          <t>PREVIBELOS</t>
-        </is>
-      </c>
-      <c r="AC22" s="3" t="inlineStr">
-        <is>
-          <t>IPASGO</t>
-        </is>
-      </c>
-      <c r="AD22" s="3" t="inlineStr">
-        <is>
-          <t>IPASGO DEPENDENTES</t>
-        </is>
-      </c>
-      <c r="AE22" s="3" t="inlineStr">
-        <is>
-          <t>BB - BRASIL</t>
-        </is>
-      </c>
-      <c r="AF22" s="3" t="inlineStr">
-        <is>
-          <t>DEVOLUÇÃO DE AD. 13°</t>
-        </is>
-      </c>
-      <c r="AG22" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL DO EVENTO</t>
-        </is>
-      </c>
+    <row r="22">
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="N22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="P22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="Q22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="R22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="S22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="T22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="U22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="V22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="X22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="Y22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="Z22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="AA22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="AB22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="AC22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="AD22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="AE22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="AF22" s="9" t="inlineStr">
+        <is>
+          <t>FUNDEB 70%</t>
+        </is>
+      </c>
+      <c r="AG22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="8" t="n"/>
+      <c r="N23" s="8" t="n"/>
+      <c r="O23" s="8" t="n"/>
+      <c r="P23" s="8" t="n"/>
+      <c r="Q23" s="8" t="n"/>
+      <c r="R23" s="8" t="n"/>
+      <c r="S23" s="8" t="n"/>
+      <c r="T23" s="8" t="n"/>
+      <c r="U23" s="8" t="n"/>
+      <c r="V23" s="8" t="n"/>
+      <c r="W23" s="8" t="n"/>
+      <c r="X23" s="8" t="n"/>
+      <c r="Y23" s="8" t="n"/>
+      <c r="Z23" s="8" t="n"/>
+      <c r="AA23" s="8" t="n"/>
+      <c r="AB23" s="8" t="n"/>
+      <c r="AC23" s="8" t="n"/>
+      <c r="AD23" s="8" t="n"/>
+      <c r="AE23" s="8" t="n"/>
+      <c r="AF23" s="8" t="n"/>
+      <c r="AG23" s="8" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>ARSEM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>CEF</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>IRRF S/ 13º SALÁRIO</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>IR</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>SINTEGO</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>SINDSAUDE</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>ITAU</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>BRADESCO</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>FUNPRECOR</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>SINDCASE</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>INSS S/ 13º SALÁRIO</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>INSS</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>IPARV</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>FUNPREV</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>FUMPRU</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>DETERMINAÇÃO JUDICIAL</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>EMP. PREV.</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>PREVPLAN</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t>IPASI</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>PARAUNAPREV</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>BRASILPREV</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>PREVJUS</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>AURIPREVI</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>FUNPRES</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>PREVFAINA</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>PALMEIRASPREV</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>PREVIBELOS</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>IPASGO</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr">
+        <is>
+          <t>IPASGO DEPENDENTES</t>
+        </is>
+      </c>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>BB - BRASIL</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>DEVOLUÇÃO DE AD. 13°</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL DO EVENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>TOTAL GERAL</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(B10,B19)</f>
-        <v/>
-      </c>
-      <c r="C23" s="7">
-        <f>SUM(C10,C19)</f>
-        <v/>
-      </c>
-      <c r="D23" s="7">
-        <f>SUM(D10,D19)</f>
-        <v/>
-      </c>
-      <c r="E23" s="7">
-        <f>SUM(E10,E19)</f>
-        <v/>
-      </c>
-      <c r="F23" s="7">
-        <f>SUM(F10,F19)</f>
-        <v/>
-      </c>
-      <c r="G23" s="7">
-        <f>SUM(G10,G19)</f>
-        <v/>
-      </c>
-      <c r="H23" s="7">
-        <f>SUM(H10,H19)</f>
-        <v/>
-      </c>
-      <c r="I23" s="7">
-        <f>SUM(I10,I19)</f>
-        <v/>
-      </c>
-      <c r="J23" s="7">
-        <f>SUM(J10,J19)</f>
-        <v/>
-      </c>
-      <c r="K23" s="7">
-        <f>SUM(K10,K19)</f>
-        <v/>
-      </c>
-      <c r="L23" s="7">
-        <f>SUM(L10,L19)</f>
-        <v/>
-      </c>
-      <c r="M23" s="7">
-        <f>SUM(M10,M19)</f>
-        <v/>
-      </c>
-      <c r="N23" s="7">
-        <f>SUM(N10,N19)</f>
-        <v/>
-      </c>
-      <c r="O23" s="7">
-        <f>SUM(O10,O19)</f>
-        <v/>
-      </c>
-      <c r="P23" s="7">
-        <f>SUM(P10,P19)</f>
-        <v/>
-      </c>
-      <c r="Q23" s="7">
-        <f>SUM(Q10,Q19)</f>
-        <v/>
-      </c>
-      <c r="R23" s="7">
-        <f>SUM(R10,R19)</f>
-        <v/>
-      </c>
-      <c r="S23" s="7">
-        <f>SUM(S10,S19)</f>
-        <v/>
-      </c>
-      <c r="T23" s="7">
-        <f>SUM(T10,T19)</f>
-        <v/>
-      </c>
-      <c r="U23" s="7">
-        <f>SUM(U10,U19)</f>
-        <v/>
-      </c>
-      <c r="V23" s="7">
-        <f>SUM(V10,V19)</f>
-        <v/>
-      </c>
-      <c r="W23" s="7">
-        <f>SUM(W10,W19)</f>
-        <v/>
-      </c>
-      <c r="X23" s="7">
-        <f>SUM(X10,X19)</f>
-        <v/>
-      </c>
-      <c r="Y23" s="7">
-        <f>SUM(Y10,Y19)</f>
-        <v/>
-      </c>
-      <c r="Z23" s="7">
-        <f>SUM(Z10,Z19)</f>
-        <v/>
-      </c>
-      <c r="AA23" s="7">
-        <f>SUM(AA10,AA19)</f>
-        <v/>
-      </c>
-      <c r="AB23" s="7">
-        <f>SUM(AB10,AB19)</f>
-        <v/>
-      </c>
-      <c r="AC23" s="7">
-        <f>SUM(AC10,AC19)</f>
-        <v/>
-      </c>
-      <c r="AD23" s="7">
-        <f>SUM(AD10,AD19)</f>
-        <v/>
-      </c>
-      <c r="AE23" s="7">
-        <f>SUM(AE10,AE19)</f>
-        <v/>
-      </c>
-      <c r="AF23" s="7">
-        <f>SUM(AF10,AF19)</f>
-        <v/>
-      </c>
-      <c r="AG23" s="7">
-        <f>SUM(B23:AF23)</f>
+      <c r="B25" s="7">
+        <f>SUM(B11,B21)</f>
+        <v/>
+      </c>
+      <c r="C25" s="7">
+        <f>SUM(C11,C21)</f>
+        <v/>
+      </c>
+      <c r="D25" s="7">
+        <f>SUM(D11,D21)</f>
+        <v/>
+      </c>
+      <c r="E25" s="7">
+        <f>SUM(E11,E21)</f>
+        <v/>
+      </c>
+      <c r="F25" s="7">
+        <f>SUM(F11,F21)</f>
+        <v/>
+      </c>
+      <c r="G25" s="7">
+        <f>SUM(G11,G21)</f>
+        <v/>
+      </c>
+      <c r="H25" s="7">
+        <f>SUM(H11,H21)</f>
+        <v/>
+      </c>
+      <c r="I25" s="7">
+        <f>SUM(I11,I21)</f>
+        <v/>
+      </c>
+      <c r="J25" s="7">
+        <f>SUM(J11,J21)</f>
+        <v/>
+      </c>
+      <c r="K25" s="7">
+        <f>SUM(K11,K21)</f>
+        <v/>
+      </c>
+      <c r="L25" s="7">
+        <f>SUM(L11,L21)</f>
+        <v/>
+      </c>
+      <c r="M25" s="7">
+        <f>SUM(M11,M21)</f>
+        <v/>
+      </c>
+      <c r="N25" s="7">
+        <f>SUM(N11,N21)</f>
+        <v/>
+      </c>
+      <c r="O25" s="7">
+        <f>SUM(O11,O21)</f>
+        <v/>
+      </c>
+      <c r="P25" s="7">
+        <f>SUM(P11,P21)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="7">
+        <f>SUM(Q11,Q21)</f>
+        <v/>
+      </c>
+      <c r="R25" s="7">
+        <f>SUM(R11,R21)</f>
+        <v/>
+      </c>
+      <c r="S25" s="7">
+        <f>SUM(S11,S21)</f>
+        <v/>
+      </c>
+      <c r="T25" s="7">
+        <f>SUM(T11,T21)</f>
+        <v/>
+      </c>
+      <c r="U25" s="7">
+        <f>SUM(U11,U21)</f>
+        <v/>
+      </c>
+      <c r="V25" s="7">
+        <f>SUM(V11,V21)</f>
+        <v/>
+      </c>
+      <c r="W25" s="7">
+        <f>SUM(W11,W21)</f>
+        <v/>
+      </c>
+      <c r="X25" s="7">
+        <f>SUM(X11,X21)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="7">
+        <f>SUM(Y11,Y21)</f>
+        <v/>
+      </c>
+      <c r="Z25" s="7">
+        <f>SUM(Z11,Z21)</f>
+        <v/>
+      </c>
+      <c r="AA25" s="7">
+        <f>SUM(AA11,AA21)</f>
+        <v/>
+      </c>
+      <c r="AB25" s="7">
+        <f>SUM(AB11,AB21)</f>
+        <v/>
+      </c>
+      <c r="AC25" s="7">
+        <f>SUM(AC11,AC21)</f>
+        <v/>
+      </c>
+      <c r="AD25" s="7">
+        <f>SUM(AD11,AD21)</f>
+        <v/>
+      </c>
+      <c r="AE25" s="7">
+        <f>SUM(AE11,AE21)</f>
+        <v/>
+      </c>
+      <c r="AF25" s="7">
+        <f>SUM(AF11,AF21)</f>
+        <v/>
+      </c>
+      <c r="AG25" s="7">
+        <f>SUM(B25:AF25)</f>
         <v/>
       </c>
     </row>
-    <row r="24"/>
+    <row r="26"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:AG1"/>
     <mergeCell ref="A3:AG3"/>
     <mergeCell ref="A4:AG4"/>
     <mergeCell ref="A2:AG2"/>
-    <mergeCell ref="A13:AG13"/>
+    <mergeCell ref="A14:AG14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape"/>
